--- a/國軍軍購案執行中個案管制表(範例).xlsx
+++ b/國軍軍購案執行中個案管制表(範例).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyzhu\Desktop\電腦小組\1150615研析試作區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC132AF8-2C61-4CAC-A87B-3EF8740C9369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AFE6AB-52E8-4AAD-A387-A85BBEFB72A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{A3D9305F-6A72-4EB0-884D-54554B853FCB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>項次</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -282,6 +282,22 @@
   <si>
     <t>待平衡支付值
 美元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TWBZEA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央、陸軍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陸軍主計處、國防部憲兵指揮部本部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>獵鳥專案</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -370,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -396,6 +412,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -713,12 +741,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C7165C-5FEB-433E-8E37-8D06574C010F}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="9" width="17.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -853,14 +882,14 @@
         <v>41672691</v>
       </c>
       <c r="J3" s="6">
-        <f t="shared" ref="J3:J15" si="0">I3/H3</f>
+        <f t="shared" ref="J3:J16" si="0">I3/H3</f>
         <v>0.86818106250000004</v>
       </c>
       <c r="K3" s="4">
         <v>40316756.359999999</v>
       </c>
       <c r="L3" s="6">
-        <f t="shared" ref="L3:L15" si="1">K3/I3</f>
+        <f t="shared" ref="L3:L16" si="1">K3/I3</f>
         <v>0.96746227307470978</v>
       </c>
       <c r="M3" s="4">
@@ -1496,6 +1525,58 @@
         <v>98023</v>
       </c>
       <c r="P15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>446</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="10">
+        <v>450111</v>
+      </c>
+      <c r="H16" s="8">
+        <v>56842784</v>
+      </c>
+      <c r="I16" s="8">
+        <v>31223812.82</v>
+      </c>
+      <c r="J16" s="11">
+        <f t="shared" si="0"/>
+        <v>0.54930125906570659</v>
+      </c>
+      <c r="K16" s="8">
+        <v>56483.63</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="1"/>
+        <v>1.8089920768363098E-3</v>
+      </c>
+      <c r="M16" s="8">
+        <v>31167329.190000001</v>
+      </c>
+      <c r="N16" s="12">
+        <v>957072149</v>
+      </c>
+      <c r="O16" s="8">
+        <v>31223812.82</v>
+      </c>
+      <c r="P16" s="8">
         <v>0</v>
       </c>
     </row>
